--- a/規格表建檔 spec-data-entry.xlsx
+++ b/規格表建檔 spec-data-entry.xlsx
@@ -23,8 +23,6 @@
     <sheet name="ST 彈簧蝴蝶" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="PT 塑膠蝴蝶" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="RN 橡膠帽" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="PC 管夾" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="CL 電纜夾" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="110">
   <si>
     <r>
       <rPr>
@@ -764,50 +762,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">PC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">管夾　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pipe-clips</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CL</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">電纜夾　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cable-clips</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">金屬敲擊式錨栓</t>
   </si>
   <si>
@@ -822,21 +776,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">MHD FLAT HEAD - BZP</t>
     </r>
     <r>
       <rPr>
@@ -1073,21 +1017,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">MHD MUSHROOM HEAD</t>
     </r>
     <r>
       <rPr>
@@ -1148,21 +1082,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Mhd Mushroom Head</t>
+      <t xml:space="preserve">MHD MUSHROOM HEAD - BLACK PHOSPHATE</t>
     </r>
     <r>
       <rPr>
@@ -1223,21 +1147,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Mhd Mushroom Head - Black Phosphate</t>
+      <t xml:space="preserve">MHD FORMING - BZP</t>
     </r>
     <r>
       <rPr>
@@ -1258,7 +1172,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">metal-hammer-drive-anchor-var3.png</t>
+      <t xml:space="preserve">metal-hammer-drive-anchor-var4.png</t>
     </r>
     <r>
       <rPr>
@@ -1279,7 +1193,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14 </t>
+      <t xml:space="preserve">4 </t>
     </r>
     <r>
       <rPr>
@@ -1293,16 +1207,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -1312,7 +1216,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Mhd Forming - Bzp</t>
+      <t xml:space="preserve">MHD OVERHEAD THREAD - BZP</t>
     </r>
     <r>
       <rPr>
@@ -1333,7 +1237,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">metal-hammer-drive-anchor-var4.png</t>
+      <t xml:space="preserve">metal-hammer-drive-anchor-var5.png</t>
     </r>
     <r>
       <rPr>
@@ -1354,7 +1258,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4 </t>
+      <t xml:space="preserve">2 </t>
     </r>
     <r>
       <rPr>
@@ -1368,16 +1272,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -1387,82 +1281,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Mhd Overhead Thread - Bzp</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">metal-hammer-drive-anchor-var5.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mhd Tie Wire - Bzp</t>
+      <t xml:space="preserve">MHD TIE WIRE - BZP</t>
     </r>
     <r>
       <rPr>
@@ -1526,21 +1345,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">NYLON NAIL-IN FLAT HD</t>
     </r>
     <r>
       <rPr>
@@ -1601,21 +1410,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">NYLON NAIL-IN ROUND HD</t>
     </r>
     <r>
       <rPr>
@@ -1676,21 +1475,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">NYLON NAIL-IN MUSHROOM HD</t>
     </r>
     <r>
       <rPr>
@@ -1930,21 +1719,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">HEX NUT TYPE</t>
     </r>
     <r>
       <rPr>
@@ -2005,21 +1784,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Hex Bolt Type</t>
+      <t xml:space="preserve">HEX BOLT TYPE</t>
     </r>
     <r>
       <rPr>
@@ -2080,21 +1849,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Eye &amp; Hook Type</t>
+      <t xml:space="preserve">EYE &amp; HOOK TYPE</t>
     </r>
     <r>
       <rPr>
@@ -2334,21 +2093,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Drop-In Anchor Bzp - Non Lipped</t>
+      <t xml:space="preserve">DROP-IN ANCHOR BZP - NON LIPPED</t>
     </r>
     <r>
       <rPr>
@@ -2409,21 +2158,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Drop-In Anchor A2-304 Stainless Steel - Non Lipped</t>
+      <t xml:space="preserve">DROP-IN ANCHOR A2-304 STAINLESS STEEL - NON LIPPED</t>
     </r>
     <r>
       <rPr>
@@ -2484,21 +2223,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Drop-In Anchor A4-316 Stainless Steel - Non Lipped</t>
+      <t xml:space="preserve">DROP-IN ANCHOR A4-316 STAINLESS STEEL - NON LIPPED</t>
     </r>
     <r>
       <rPr>
@@ -2559,21 +2288,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Drop-In Anchor Bzp - Lipped</t>
+      <t xml:space="preserve">DROP-IN ANCHOR BZP - LIPPED</t>
     </r>
     <r>
       <rPr>
@@ -2765,21 +2484,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">CONCRETE BOLT - PAN HEAD</t>
     </r>
     <r>
       <rPr>
@@ -2840,96 +2549,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">concrete-boltpan-csk-head-spec2.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Concrete Bolt - Csk Head</t>
+      <t xml:space="preserve">CONCRETE BOLT - CSK HEAD</t>
     </r>
     <r>
       <rPr>
@@ -3071,21 +2695,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">SPRING TOGGLE</t>
     </r>
     <r>
       <rPr>
@@ -3146,21 +2760,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">SPRING TOGGLE (WING ONLY)</t>
     </r>
     <r>
       <rPr>
@@ -3224,21 +2828,11 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">PLASTIC TOGGLE ANCHOR - PTA1</t>
     </r>
     <r>
       <rPr>
@@ -3259,7 +2853,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">plastic-toggle-anchor-spec1.png</t>
+      <t xml:space="preserve">plastic-toggle-anchor-var1.png</t>
     </r>
     <r>
       <rPr>
@@ -3280,7 +2874,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13 </t>
+      <t xml:space="preserve">3 </t>
     </r>
     <r>
       <rPr>
@@ -3294,16 +2888,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -3313,7 +2897,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Plastic Toggle Anchor - PTA1</t>
+      <t xml:space="preserve">PLASTIC TOGGLE ANCHOR - PTA2</t>
     </r>
     <r>
       <rPr>
@@ -3334,7 +2918,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">plastic-toggle-anchor-var1.png</t>
+      <t xml:space="preserve">plastic-toggle-anchor-var2.png</t>
     </r>
     <r>
       <rPr>
@@ -3355,7 +2939,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3 </t>
+      <t xml:space="preserve">6 </t>
     </r>
     <r>
       <rPr>
@@ -3369,16 +2953,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -3388,82 +2962,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Plastic Toggle Anchor - PTA2</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">plastic-toggle-anchor-var2.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">變體：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Plastic Toggle Anchor - PTA3</t>
+      <t xml:space="preserve">PLASTIC TOGGLE ANCHOR - PTA3</t>
     </r>
     <r>
       <rPr>
@@ -3659,462 +3158,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">14 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">管夾</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pipe-clips-spec1.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pipe-clips-spec2.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">電纜夾</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cable-clips-spec1.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cable-clips-spec2.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cable-clips-spec3.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">規格表 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cable-clips-spec4.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF0233A0"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8 </t>
     </r>
     <r>
       <rPr>
@@ -4251,16 +3294,16 @@
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FF0233A0"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FF0233A0"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -4375,7 +3418,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4457,6 +3500,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4655,8 +3702,8 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>182880</xdr:rowOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>78120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4670,43 +3717,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="352440" y="24193440"/>
-          <a:ext cx="8572320" cy="3895200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>166</xdr:row>
-      <xdr:rowOff>97920</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>174</xdr:row>
-      <xdr:rowOff>22320</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 5" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="32004000"/>
           <a:ext cx="8572320" cy="1504440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4723,27 +3733,27 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>183</xdr:row>
-      <xdr:rowOff>42120</xdr:rowOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>97920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>188</xdr:row>
-      <xdr:rowOff>71640</xdr:rowOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>127440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 6" descr="Picture"/>
+        <xdr:cNvPr id="4" name="Image 5" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
+        <a:blip r:embed="rId5"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="352440" y="35242560"/>
+          <a:off x="352440" y="27432000"/>
           <a:ext cx="8572320" cy="1037880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4760,27 +3770,27 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>195</xdr:row>
-      <xdr:rowOff>176400</xdr:rowOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>41760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>201</xdr:row>
-      <xdr:rowOff>15480</xdr:rowOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>71280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 7" descr="Picture"/>
+        <xdr:cNvPr id="5" name="Image 6" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
+        <a:blip r:embed="rId6"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="352440" y="37719000"/>
+          <a:off x="352440" y="29908440"/>
           <a:ext cx="8572320" cy="1037880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4813,7 +3823,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="21" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4845,12 +3855,12 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>170640</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>37080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Image 2" descr="Picture"/>
+        <xdr:cNvPr id="22" name="Image 2" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4860,43 +3870,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="352440" y="6477120"/>
-          <a:ext cx="8572320" cy="6114600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>151920</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>171720</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Image 3" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="18097560"/>
           <a:ext cx="8572320" cy="2933280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4929,7 +3902,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="23" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4971,7 +3944,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="24" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5008,7 +3981,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Image 2" descr="Picture"/>
+        <xdr:cNvPr id="25" name="Image 2" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5045,12 +4018,12 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>27000</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>112680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="26" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5060,43 +4033,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="352440" y="762120"/>
-          <a:ext cx="8572320" cy="4142880"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>75240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Image 2" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="8572680"/>
           <a:ext cx="8572320" cy="1371240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5113,27 +4049,27 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>74880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>20160</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>75960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Image 3" descr="Picture"/>
+        <xdr:cNvPr id="27" name="Image 2" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="352440" y="11620440"/>
+          <a:off x="352440" y="3809880"/>
           <a:ext cx="8572320" cy="2152440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5150,27 +4086,27 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>153720</xdr:rowOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>19080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>135360</xdr:rowOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Image 4" descr="Picture"/>
+        <xdr:cNvPr id="28" name="Image 3" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <a:blip r:embed="rId3"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="352440" y="16002000"/>
+          <a:off x="352440" y="8191440"/>
           <a:ext cx="8572320" cy="1371240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5203,7 +4139,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="29" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5240,7 +4176,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Image 2" descr="Picture"/>
+        <xdr:cNvPr id="30" name="Image 2" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5251,238 +4187,6 @@
         <a:xfrm>
           <a:off x="352440" y="8381880"/>
           <a:ext cx="8572320" cy="4114440"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>131040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="762120"/>
-          <a:ext cx="8572320" cy="4228920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>74880</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>85320</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Image 2" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="8191440"/>
-          <a:ext cx="8572320" cy="1590480"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>131040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>160200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="762120"/>
-          <a:ext cx="8572320" cy="2561760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>74880</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>18720</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Image 2" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="5524560"/>
-          <a:ext cx="8572320" cy="3238200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>96120</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Image 3" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="11430000"/>
-          <a:ext cx="8572320" cy="5466960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>153720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255240</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>97200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Image 4" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="352440" y="20954880"/>
-          <a:ext cx="8572320" cy="3238200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5514,7 +4218,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="6" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5551,7 +4255,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 2" descr="Picture"/>
+        <xdr:cNvPr id="7" name="Image 2" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5588,7 +4292,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Image 3" descr="Picture"/>
+        <xdr:cNvPr id="8" name="Image 3" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5630,7 +4334,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="9" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5672,7 +4376,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="10" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5714,7 +4418,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="11" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5751,7 +4455,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Image 2" descr="Picture"/>
+        <xdr:cNvPr id="12" name="Image 2" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5788,7 +4492,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Image 3" descr="Picture"/>
+        <xdr:cNvPr id="13" name="Image 3" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5830,7 +4534,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="14" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5872,7 +4576,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="15" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5914,7 +4618,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="16" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5951,7 +4655,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Image 2" descr="Picture"/>
+        <xdr:cNvPr id="17" name="Image 2" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5988,7 +4692,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Image 3" descr="Picture"/>
+        <xdr:cNvPr id="18" name="Image 3" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6025,7 +4729,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Image 4" descr="Picture"/>
+        <xdr:cNvPr id="19" name="Image 4" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6067,7 +4771,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="20" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6272,7 +4976,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -6511,22 +5215,6 @@
       </c>
       <c r="B34" s="8" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -6557,7 +5245,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6568,53 +5256,53 @@
         <v>31</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>99</v>
+        <v>53</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="F65" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="G65" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="H65" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="I65" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F65" s="16" t="s">
+      <c r="J65" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G65" s="16" t="s">
+      <c r="K65" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="L65" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I65" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J65" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K65" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L65" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7375,7 +6063,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -7387,7 +6075,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7398,53 +6086,53 @@
         <v>39</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="F21" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="G21" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="H21" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="I21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="J21" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="K21" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="L21" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7639,701 +6327,237 @@
     </row>
     <row r="34" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="15" t="s">
+      <c r="D52" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="F52" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="G52" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="16" t="s">
+      <c r="H52" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E70" s="16" t="s">
+      <c r="I52" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F70" s="16" t="s">
+      <c r="J52" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G70" s="16" t="s">
+      <c r="K52" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="L52" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I70" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J70" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K70" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L70" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="17" t="n">
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-      <c r="L71" s="19" t="str">
-        <f aca="false">IF(OR(D71="",E71=""),"",IF(D71&lt;&gt;INT(D71),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D71,"00")&amp;TEXT(E71,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="17" t="n">
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="19" t="str">
+        <f aca="false">IF(OR(D53="",E53=""),"",IF(D53&lt;&gt;INT(D53),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D53,"00")&amp;TEXT(E53,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="18"/>
-      <c r="H72" s="18"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="18"/>
-      <c r="L72" s="19" t="str">
-        <f aca="false">IF(OR(D72="",E72=""),"",IF(D72&lt;&gt;INT(D72),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D72,"00")&amp;TEXT(E72,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="17" t="n">
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="19" t="str">
+        <f aca="false">IF(OR(D54="",E54=""),"",IF(D54&lt;&gt;INT(D54),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D54,"00")&amp;TEXT(E54,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="18"/>
-      <c r="H73" s="18"/>
-      <c r="I73" s="18"/>
-      <c r="J73" s="18"/>
-      <c r="K73" s="18"/>
-      <c r="L73" s="19" t="str">
-        <f aca="false">IF(OR(D73="",E73=""),"",IF(D73&lt;&gt;INT(D73),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D73,"00")&amp;TEXT(E73,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="17" t="n">
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="19" t="str">
+        <f aca="false">IF(OR(D55="",E55=""),"",IF(D55&lt;&gt;INT(D55),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D55,"00")&amp;TEXT(E55,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="18"/>
-      <c r="I74" s="18"/>
-      <c r="J74" s="18"/>
-      <c r="K74" s="18"/>
-      <c r="L74" s="19" t="str">
-        <f aca="false">IF(OR(D74="",E74=""),"",IF(D74&lt;&gt;INT(D74),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D74,"00")&amp;TEXT(E74,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="17" t="n">
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="19" t="str">
+        <f aca="false">IF(OR(D56="",E56=""),"",IF(D56&lt;&gt;INT(D56),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D56,"00")&amp;TEXT(E56,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
-      <c r="H75" s="18"/>
-      <c r="I75" s="18"/>
-      <c r="J75" s="18"/>
-      <c r="K75" s="18"/>
-      <c r="L75" s="19" t="str">
-        <f aca="false">IF(OR(D75="",E75=""),"",IF(D75&lt;&gt;INT(D75),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D75,"00")&amp;TEXT(E75,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="17" t="n">
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="19" t="str">
+        <f aca="false">IF(OR(D57="",E57=""),"",IF(D57&lt;&gt;INT(D57),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D57,"00")&amp;TEXT(E57,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="18"/>
-      <c r="H76" s="18"/>
-      <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="19" t="str">
-        <f aca="false">IF(OR(D76="",E76=""),"",IF(D76&lt;&gt;INT(D76),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D76,"00")&amp;TEXT(E76,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="17" t="n">
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="19" t="str">
+        <f aca="false">IF(OR(D58="",E58=""),"",IF(D58&lt;&gt;INT(D58),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D58,"00")&amp;TEXT(E58,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="18"/>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="19" t="str">
-        <f aca="false">IF(OR(D77="",E77=""),"",IF(D77&lt;&gt;INT(D77),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D77,"00")&amp;TEXT(E77,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="17" t="n">
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="19" t="str">
+        <f aca="false">IF(OR(D59="",E59=""),"",IF(D59&lt;&gt;INT(D59),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D59,"00")&amp;TEXT(E59,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="18"/>
-      <c r="H78" s="18"/>
-      <c r="I78" s="18"/>
-      <c r="J78" s="18"/>
-      <c r="K78" s="18"/>
-      <c r="L78" s="19" t="str">
-        <f aca="false">IF(OR(D78="",E78=""),"",IF(D78&lt;&gt;INT(D78),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D78,"00")&amp;TEXT(E78,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="17" t="n">
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="19" t="str">
+        <f aca="false">IF(OR(D60="",E60=""),"",IF(D60&lt;&gt;INT(D60),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D60,"00")&amp;TEXT(E60,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="18"/>
-      <c r="H79" s="18"/>
-      <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
-      <c r="K79" s="18"/>
-      <c r="L79" s="19" t="str">
-        <f aca="false">IF(OR(D79="",E79=""),"",IF(D79&lt;&gt;INT(D79),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D79,"00")&amp;TEXT(E79,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="17" t="n">
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="19" t="str">
+        <f aca="false">IF(OR(D61="",E61=""),"",IF(D61&lt;&gt;INT(D61),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D61,"00")&amp;TEXT(E61,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="18"/>
-      <c r="H80" s="18"/>
-      <c r="I80" s="18"/>
-      <c r="J80" s="18"/>
-      <c r="K80" s="18"/>
-      <c r="L80" s="19" t="str">
-        <f aca="false">IF(OR(D80="",E80=""),"",IF(D80&lt;&gt;INT(D80),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D80,"00")&amp;TEXT(E80,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-      <c r="H81" s="18"/>
-      <c r="I81" s="18"/>
-      <c r="J81" s="18"/>
-      <c r="K81" s="18"/>
-      <c r="L81" s="19" t="str">
-        <f aca="false">IF(OR(D81="",E81=""),"",IF(D81&lt;&gt;INT(D81),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D81,"00")&amp;TEXT(E81,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="18"/>
-      <c r="H82" s="18"/>
-      <c r="I82" s="18"/>
-      <c r="J82" s="18"/>
-      <c r="K82" s="18"/>
-      <c r="L82" s="19" t="str">
-        <f aca="false">IF(OR(D82="",E82=""),"",IF(D82&lt;&gt;INT(D82),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D82,"00")&amp;TEXT(E82,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="18"/>
-      <c r="H83" s="18"/>
-      <c r="I83" s="18"/>
-      <c r="J83" s="18"/>
-      <c r="K83" s="18"/>
-      <c r="L83" s="19" t="str">
-        <f aca="false">IF(OR(D83="",E83=""),"",IF(D83&lt;&gt;INT(D83),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D83,"00")&amp;TEXT(E83,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B84" s="18"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="18"/>
-      <c r="E84" s="18"/>
-      <c r="F84" s="18"/>
-      <c r="G84" s="18"/>
-      <c r="H84" s="18"/>
-      <c r="I84" s="18"/>
-      <c r="J84" s="18"/>
-      <c r="K84" s="18"/>
-      <c r="L84" s="19" t="str">
-        <f aca="false">IF(OR(D84="",E84=""),"",IF(D84&lt;&gt;INT(D84),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D84,"00")&amp;TEXT(E84,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="18"/>
-      <c r="H85" s="18"/>
-      <c r="I85" s="18"/>
-      <c r="J85" s="18"/>
-      <c r="K85" s="18"/>
-      <c r="L85" s="19" t="str">
-        <f aca="false">IF(OR(D85="",E85=""),"",IF(D85&lt;&gt;INT(D85),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D85,"00")&amp;TEXT(E85,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B86" s="18"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
-      <c r="F86" s="18"/>
-      <c r="G86" s="18"/>
-      <c r="H86" s="18"/>
-      <c r="I86" s="18"/>
-      <c r="J86" s="18"/>
-      <c r="K86" s="18"/>
-      <c r="L86" s="19" t="str">
-        <f aca="false">IF(OR(D86="",E86=""),"",IF(D86&lt;&gt;INT(D86),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D86,"00")&amp;TEXT(E86,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="18"/>
-      <c r="I87" s="18"/>
-      <c r="J87" s="18"/>
-      <c r="K87" s="18"/>
-      <c r="L87" s="19" t="str">
-        <f aca="false">IF(OR(D87="",E87=""),"",IF(D87&lt;&gt;INT(D87),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D87,"00")&amp;TEXT(E87,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="18"/>
-      <c r="J88" s="18"/>
-      <c r="K88" s="18"/>
-      <c r="L88" s="19" t="str">
-        <f aca="false">IF(OR(D88="",E88=""),"",IF(D88&lt;&gt;INT(D88),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D88,"00")&amp;TEXT(E88,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-      <c r="H89" s="18"/>
-      <c r="I89" s="18"/>
-      <c r="J89" s="18"/>
-      <c r="K89" s="18"/>
-      <c r="L89" s="19" t="str">
-        <f aca="false">IF(OR(D89="",E89=""),"",IF(D89&lt;&gt;INT(D89),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D89,"00")&amp;TEXT(E89,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="B90" s="18"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="18"/>
-      <c r="E90" s="18"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
-      <c r="H90" s="18"/>
-      <c r="I90" s="18"/>
-      <c r="J90" s="18"/>
-      <c r="K90" s="18"/>
-      <c r="L90" s="19" t="str">
-        <f aca="false">IF(OR(D90="",E90=""),"",IF(D90&lt;&gt;INT(D90),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D90,"00")&amp;TEXT(E90,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="18"/>
-      <c r="I91" s="18"/>
-      <c r="J91" s="18"/>
-      <c r="K91" s="18"/>
-      <c r="L91" s="19" t="str">
-        <f aca="false">IF(OR(D91="",E91=""),"",IF(D91&lt;&gt;INT(D91),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D91,"00")&amp;TEXT(E91,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="18"/>
-      <c r="H92" s="18"/>
-      <c r="I92" s="18"/>
-      <c r="J92" s="18"/>
-      <c r="K92" s="18"/>
-      <c r="L92" s="19" t="str">
-        <f aca="false">IF(OR(D92="",E92=""),"",IF(D92&lt;&gt;INT(D92),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D92,"00")&amp;TEXT(E92,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B113" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C113" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D113" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E113" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F113" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G113" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H113" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I113" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J113" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K113" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L113" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B114" s="18"/>
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
-      <c r="F114" s="18"/>
-      <c r="G114" s="18"/>
-      <c r="H114" s="18"/>
-      <c r="I114" s="18"/>
-      <c r="J114" s="18"/>
-      <c r="K114" s="18"/>
-      <c r="L114" s="19" t="str">
-        <f aca="false">IF(OR(D114="",E114=""),"",IF(D114&lt;&gt;INT(D114),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D114,"00")&amp;TEXT(E114,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B115" s="18"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="18"/>
-      <c r="F115" s="18"/>
-      <c r="G115" s="18"/>
-      <c r="H115" s="18"/>
-      <c r="I115" s="18"/>
-      <c r="J115" s="18"/>
-      <c r="K115" s="18"/>
-      <c r="L115" s="19" t="str">
-        <f aca="false">IF(OR(D115="",E115=""),"",IF(D115&lt;&gt;INT(D115),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D115,"00")&amp;TEXT(E115,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B116" s="18"/>
-      <c r="C116" s="18"/>
-      <c r="D116" s="18"/>
-      <c r="E116" s="18"/>
-      <c r="F116" s="18"/>
-      <c r="G116" s="18"/>
-      <c r="H116" s="18"/>
-      <c r="I116" s="18"/>
-      <c r="J116" s="18"/>
-      <c r="K116" s="18"/>
-      <c r="L116" s="19" t="str">
-        <f aca="false">IF(OR(D116="",E116=""),"",IF(D116&lt;&gt;INT(D116),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D116,"00")&amp;TEXT(E116,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B117" s="18"/>
-      <c r="C117" s="18"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="18"/>
-      <c r="F117" s="18"/>
-      <c r="G117" s="18"/>
-      <c r="H117" s="18"/>
-      <c r="I117" s="18"/>
-      <c r="J117" s="18"/>
-      <c r="K117" s="18"/>
-      <c r="L117" s="19" t="str">
-        <f aca="false">IF(OR(D117="",E117=""),"",IF(D117&lt;&gt;INT(D117),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D117,"00")&amp;TEXT(E117,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B118" s="18"/>
-      <c r="C118" s="18"/>
-      <c r="D118" s="18"/>
-      <c r="E118" s="18"/>
-      <c r="F118" s="18"/>
-      <c r="G118" s="18"/>
-      <c r="H118" s="18"/>
-      <c r="I118" s="18"/>
-      <c r="J118" s="18"/>
-      <c r="K118" s="18"/>
-      <c r="L118" s="19" t="str">
-        <f aca="false">IF(OR(D118="",E118=""),"",IF(D118&lt;&gt;INT(D118),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D118,"00")&amp;TEXT(E118,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B119" s="18"/>
-      <c r="C119" s="18"/>
-      <c r="D119" s="18"/>
-      <c r="E119" s="18"/>
-      <c r="F119" s="18"/>
-      <c r="G119" s="18"/>
-      <c r="H119" s="18"/>
-      <c r="I119" s="18"/>
-      <c r="J119" s="18"/>
-      <c r="K119" s="18"/>
-      <c r="L119" s="19" t="str">
-        <f aca="false">IF(OR(D119="",E119=""),"",IF(D119&lt;&gt;INT(D119),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D119,"00")&amp;TEXT(E119,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B120" s="18"/>
-      <c r="C120" s="18"/>
-      <c r="D120" s="18"/>
-      <c r="E120" s="18"/>
-      <c r="F120" s="18"/>
-      <c r="G120" s="18"/>
-      <c r="H120" s="18"/>
-      <c r="I120" s="18"/>
-      <c r="J120" s="18"/>
-      <c r="K120" s="18"/>
-      <c r="L120" s="19" t="str">
-        <f aca="false">IF(OR(D120="",E120=""),"",IF(D120&lt;&gt;INT(D120),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D120,"00")&amp;TEXT(E120,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B121" s="18"/>
-      <c r="C121" s="18"/>
-      <c r="D121" s="18"/>
-      <c r="E121" s="18"/>
-      <c r="F121" s="18"/>
-      <c r="G121" s="18"/>
-      <c r="H121" s="18"/>
-      <c r="I121" s="18"/>
-      <c r="J121" s="18"/>
-      <c r="K121" s="18"/>
-      <c r="L121" s="19" t="str">
-        <f aca="false">IF(OR(D121="",E121=""),"",IF(D121&lt;&gt;INT(D121),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D121,"00")&amp;TEXT(E121,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B122" s="18"/>
-      <c r="C122" s="18"/>
-      <c r="D122" s="18"/>
-      <c r="E122" s="18"/>
-      <c r="F122" s="18"/>
-      <c r="G122" s="18"/>
-      <c r="H122" s="18"/>
-      <c r="I122" s="18"/>
-      <c r="J122" s="18"/>
-      <c r="K122" s="18"/>
-      <c r="L122" s="19" t="str">
-        <f aca="false">IF(OR(D122="",E122=""),"",IF(D122&lt;&gt;INT(D122),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D122,"00")&amp;TEXT(E122,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B123" s="18"/>
-      <c r="C123" s="18"/>
-      <c r="D123" s="18"/>
-      <c r="E123" s="18"/>
-      <c r="F123" s="18"/>
-      <c r="G123" s="18"/>
-      <c r="H123" s="18"/>
-      <c r="I123" s="18"/>
-      <c r="J123" s="18"/>
-      <c r="K123" s="18"/>
-      <c r="L123" s="19" t="str">
-        <f aca="false">IF(OR(D123="",E123=""),"",IF(D123&lt;&gt;INT(D123),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D123,"00")&amp;TEXT(E123,"000")))</f>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="19" t="str">
+        <f aca="false">IF(OR(D62="",E62=""),"",IF(D62&lt;&gt;INT(D62),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D62,"00")&amp;TEXT(E62,"000")))</f>
         <v/>
       </c>
     </row>
@@ -8366,7 +6590,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8377,53 +6601,53 @@
         <v>41</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>105</v>
+        <v>53</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="F20" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="G20" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="H20" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="I20" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="J20" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="K20" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="L20" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8569,7 +6793,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8580,53 +6804,53 @@
         <v>45</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="F38" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="G38" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="H38" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="I38" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="J38" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="K38" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="L38" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L38" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9011,48 +7235,48 @@
     </row>
     <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="F75" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="G75" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D75" s="16" t="s">
+      <c r="H75" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E75" s="16" t="s">
+      <c r="I75" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F75" s="16" t="s">
+      <c r="J75" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G75" s="16" t="s">
+      <c r="K75" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H75" s="16" t="s">
+      <c r="L75" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I75" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K75" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L75" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9186,7 +7410,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -9198,7 +7422,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9209,153 +7433,161 @@
         <v>47</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="D14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="F14" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="G14" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="H14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="I14" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="J14" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="K14" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="L14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I29" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="n">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="19" t="str">
-        <f aca="false">IF(OR(D30="",E30=""),"",IF(D30&lt;&gt;INT(D30),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D30,"00")&amp;TEXT(E30,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="n">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="19" t="str">
+        <f aca="false">IF(OR(D15="",E15=""),"",IF(D15&lt;&gt;INT(D15),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D15,"00")&amp;TEXT(E15,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="19" t="str">
-        <f aca="false">IF(OR(D31="",E31=""),"",IF(D31&lt;&gt;INT(D31),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D31,"00")&amp;TEXT(E31,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="n">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="19" t="str">
+        <f aca="false">IF(OR(D16="",E16=""),"",IF(D16&lt;&gt;INT(D16),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D16,"00")&amp;TEXT(E16,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="19" t="str">
-        <f aca="false">IF(OR(D32="",E32=""),"",IF(D32&lt;&gt;INT(D32),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D32,"00")&amp;TEXT(E32,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="19" t="str">
-        <f aca="false">IF(OR(D33="",E33=""),"",IF(D33&lt;&gt;INT(D33),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D33,"00")&amp;TEXT(E33,"000")))</f>
-        <v/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="19" t="str">
+        <f aca="false">IF(OR(D17="",E17=""),"",IF(D17&lt;&gt;INT(D17),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D17,"00")&amp;TEXT(E17,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="19" t="str">
-        <f aca="false">IF(OR(D34="",E34=""),"",IF(D34&lt;&gt;INT(D34),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D34,"00")&amp;TEXT(E34,"000")))</f>
-        <v/>
+      <c r="A34" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
@@ -9374,7 +7606,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -9393,7 +7625,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
@@ -9412,7 +7644,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -9431,7 +7663,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
@@ -9450,7 +7682,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -9467,93 +7699,93 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="19" t="str">
-        <f aca="false">IF(OR(D41="",E41=""),"",IF(D41&lt;&gt;INT(D41),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D41,"00")&amp;TEXT(E41,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="19" t="str">
-        <f aca="false">IF(OR(D42="",E42=""),"",IF(D42&lt;&gt;INT(D42),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D42,"00")&amp;TEXT(E42,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
+    <row r="43" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="14" t="s">
-        <v>111</v>
+      <c r="D53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="J53" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="19" t="str">
+        <f aca="false">IF(OR(D54="",E54=""),"",IF(D54&lt;&gt;INT(D54),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D54,"00")&amp;TEXT(E54,"000")))</f>
+        <v/>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I55" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J55" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K55" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L55" s="16" t="s">
-        <v>70</v>
+      <c r="A55" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="19" t="str">
+        <f aca="false">IF(OR(D55="",E55=""),"",IF(D55&lt;&gt;INT(D55),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D55,"00")&amp;TEXT(E55,"000")))</f>
+        <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -9567,307 +7799,6 @@
       <c r="K56" s="18"/>
       <c r="L56" s="19" t="str">
         <f aca="false">IF(OR(D56="",E56=""),"",IF(D56&lt;&gt;INT(D56),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D56,"00")&amp;TEXT(E56,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="19" t="str">
-        <f aca="false">IF(OR(D57="",E57=""),"",IF(D57&lt;&gt;INT(D57),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D57,"00")&amp;TEXT(E57,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="18"/>
-      <c r="L58" s="19" t="str">
-        <f aca="false">IF(OR(D58="",E58=""),"",IF(D58&lt;&gt;INT(D58),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D58,"00")&amp;TEXT(E58,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G75" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H75" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I75" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K75" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L75" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="18"/>
-      <c r="H76" s="18"/>
-      <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="19" t="str">
-        <f aca="false">IF(OR(D76="",E76=""),"",IF(D76&lt;&gt;INT(D76),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D76,"00")&amp;TEXT(E76,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="18"/>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="19" t="str">
-        <f aca="false">IF(OR(D77="",E77=""),"",IF(D77&lt;&gt;INT(D77),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D77,"00")&amp;TEXT(E77,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="18"/>
-      <c r="H78" s="18"/>
-      <c r="I78" s="18"/>
-      <c r="J78" s="18"/>
-      <c r="K78" s="18"/>
-      <c r="L78" s="19" t="str">
-        <f aca="false">IF(OR(D78="",E78=""),"",IF(D78&lt;&gt;INT(D78),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D78,"00")&amp;TEXT(E78,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="18"/>
-      <c r="H79" s="18"/>
-      <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
-      <c r="K79" s="18"/>
-      <c r="L79" s="19" t="str">
-        <f aca="false">IF(OR(D79="",E79=""),"",IF(D79&lt;&gt;INT(D79),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D79,"00")&amp;TEXT(E79,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="18"/>
-      <c r="H80" s="18"/>
-      <c r="I80" s="18"/>
-      <c r="J80" s="18"/>
-      <c r="K80" s="18"/>
-      <c r="L80" s="19" t="str">
-        <f aca="false">IF(OR(D80="",E80=""),"",IF(D80&lt;&gt;INT(D80),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D80,"00")&amp;TEXT(E80,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-      <c r="H81" s="18"/>
-      <c r="I81" s="18"/>
-      <c r="J81" s="18"/>
-      <c r="K81" s="18"/>
-      <c r="L81" s="19" t="str">
-        <f aca="false">IF(OR(D81="",E81=""),"",IF(D81&lt;&gt;INT(D81),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D81,"00")&amp;TEXT(E81,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B94" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C94" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D94" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E94" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F94" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G94" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H94" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I94" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J94" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K94" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L94" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B95" s="18"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="18"/>
-      <c r="H95" s="18"/>
-      <c r="I95" s="18"/>
-      <c r="J95" s="18"/>
-      <c r="K95" s="18"/>
-      <c r="L95" s="19" t="str">
-        <f aca="false">IF(OR(D95="",E95=""),"",IF(D95&lt;&gt;INT(D95),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D95,"00")&amp;TEXT(E95,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B96" s="18"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="18"/>
-      <c r="E96" s="18"/>
-      <c r="F96" s="18"/>
-      <c r="G96" s="18"/>
-      <c r="H96" s="18"/>
-      <c r="I96" s="18"/>
-      <c r="J96" s="18"/>
-      <c r="K96" s="18"/>
-      <c r="L96" s="19" t="str">
-        <f aca="false">IF(OR(D96="",E96=""),"",IF(D96&lt;&gt;INT(D96),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D96,"00")&amp;TEXT(E96,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="18"/>
-      <c r="H97" s="18"/>
-      <c r="I97" s="18"/>
-      <c r="J97" s="18"/>
-      <c r="K97" s="18"/>
-      <c r="L97" s="19" t="str">
-        <f aca="false">IF(OR(D97="",E97=""),"",IF(D97&lt;&gt;INT(D97),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D97,"00")&amp;TEXT(E97,"000")))</f>
         <v/>
       </c>
     </row>
@@ -9900,7 +7831,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9911,53 +7842,53 @@
         <v>49</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>115</v>
+        <v>53</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="F28" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="G28" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="H28" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="I28" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="J28" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="K28" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H28" s="16" t="s">
+      <c r="L28" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10209,48 +8140,48 @@
     </row>
     <row r="44" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>116</v>
+        <v>53</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E69" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="F69" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="G69" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="H69" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E69" s="16" t="s">
+      <c r="I69" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F69" s="16" t="s">
+      <c r="J69" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G69" s="16" t="s">
+      <c r="K69" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="L69" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I69" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J69" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K69" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L69" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10516,1337 +8447,6 @@
       <c r="K83" s="18"/>
       <c r="L83" s="19" t="str">
         <f aca="false">IF(OR(D83="",E83=""),"",IF(D83&lt;&gt;INT(D83),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D83,"00")&amp;TEXT(E83,"000")))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:L57"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I29" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="19" t="str">
-        <f aca="false">IF(OR(D30="",E30=""),"",IF(D30&lt;&gt;INT(D30),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D30,"00")&amp;TEXT(E30,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="19" t="str">
-        <f aca="false">IF(OR(D31="",E31=""),"",IF(D31&lt;&gt;INT(D31),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D31,"00")&amp;TEXT(E31,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="19" t="str">
-        <f aca="false">IF(OR(D32="",E32=""),"",IF(D32&lt;&gt;INT(D32),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D32,"00")&amp;TEXT(E32,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="19" t="str">
-        <f aca="false">IF(OR(D33="",E33=""),"",IF(D33&lt;&gt;INT(D33),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D33,"00")&amp;TEXT(E33,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="19" t="str">
-        <f aca="false">IF(OR(D34="",E34=""),"",IF(D34&lt;&gt;INT(D34),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D34,"00")&amp;TEXT(E34,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="19" t="str">
-        <f aca="false">IF(OR(D35="",E35=""),"",IF(D35&lt;&gt;INT(D35),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D35,"00")&amp;TEXT(E35,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="19" t="str">
-        <f aca="false">IF(OR(D36="",E36=""),"",IF(D36&lt;&gt;INT(D36),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D36,"00")&amp;TEXT(E36,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="19" t="str">
-        <f aca="false">IF(OR(D37="",E37=""),"",IF(D37&lt;&gt;INT(D37),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D37,"00")&amp;TEXT(E37,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="19" t="str">
-        <f aca="false">IF(OR(D38="",E38=""),"",IF(D38&lt;&gt;INT(D38),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D38,"00")&amp;TEXT(E38,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="19" t="str">
-        <f aca="false">IF(OR(D39="",E39=""),"",IF(D39&lt;&gt;INT(D39),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D39,"00")&amp;TEXT(E39,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="19" t="str">
-        <f aca="false">IF(OR(D40="",E40=""),"",IF(D40&lt;&gt;INT(D40),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D40,"00")&amp;TEXT(E40,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F54" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I54" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J54" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K54" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L54" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="19" t="str">
-        <f aca="false">IF(OR(D55="",E55=""),"",IF(D55&lt;&gt;INT(D55),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D55,"00")&amp;TEXT(E55,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="19" t="str">
-        <f aca="false">IF(OR(D56="",E56=""),"",IF(D56&lt;&gt;INT(D56),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D56,"00")&amp;TEXT(E56,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="19" t="str">
-        <f aca="false">IF(OR(D57="",E57=""),"",IF(D57&lt;&gt;INT(D57),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D57,"00")&amp;TEXT(E57,"000")))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:L138"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="19" t="str">
-        <f aca="false">IF(OR(D21="",E21=""),"",IF(D21&lt;&gt;INT(D21),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D21,"00")&amp;TEXT(E21,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="19" t="str">
-        <f aca="false">IF(OR(D22="",E22=""),"",IF(D22&lt;&gt;INT(D22),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D22,"00")&amp;TEXT(E22,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="19" t="str">
-        <f aca="false">IF(OR(D23="",E23=""),"",IF(D23&lt;&gt;INT(D23),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D23,"00")&amp;TEXT(E23,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="19" t="str">
-        <f aca="false">IF(OR(D24="",E24=""),"",IF(D24&lt;&gt;INT(D24),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D24,"00")&amp;TEXT(E24,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="19" t="str">
-        <f aca="false">IF(OR(D25="",E25=""),"",IF(D25&lt;&gt;INT(D25),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D25,"00")&amp;TEXT(E25,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="19" t="str">
-        <f aca="false">IF(OR(D26="",E26=""),"",IF(D26&lt;&gt;INT(D26),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D26,"00")&amp;TEXT(E26,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I49" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J49" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K49" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L49" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="19" t="str">
-        <f aca="false">IF(OR(D50="",E50=""),"",IF(D50&lt;&gt;INT(D50),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D50,"00")&amp;TEXT(E50,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="19" t="str">
-        <f aca="false">IF(OR(D51="",E51=""),"",IF(D51&lt;&gt;INT(D51),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D51,"00")&amp;TEXT(E51,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B52" s="18"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="19" t="str">
-        <f aca="false">IF(OR(D52="",E52=""),"",IF(D52&lt;&gt;INT(D52),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D52,"00")&amp;TEXT(E52,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="19" t="str">
-        <f aca="false">IF(OR(D53="",E53=""),"",IF(D53&lt;&gt;INT(D53),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D53,"00")&amp;TEXT(E53,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="19" t="str">
-        <f aca="false">IF(OR(D54="",E54=""),"",IF(D54&lt;&gt;INT(D54),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D54,"00")&amp;TEXT(E54,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="19" t="str">
-        <f aca="false">IF(OR(D55="",E55=""),"",IF(D55&lt;&gt;INT(D55),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D55,"00")&amp;TEXT(E55,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="19" t="str">
-        <f aca="false">IF(OR(D56="",E56=""),"",IF(D56&lt;&gt;INT(D56),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D56,"00")&amp;TEXT(E56,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="19" t="str">
-        <f aca="false">IF(OR(D57="",E57=""),"",IF(D57&lt;&gt;INT(D57),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D57,"00")&amp;TEXT(E57,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B92" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D92" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E92" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F92" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G92" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H92" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I92" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J92" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K92" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L92" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="18"/>
-      <c r="I93" s="18"/>
-      <c r="J93" s="18"/>
-      <c r="K93" s="18"/>
-      <c r="L93" s="19" t="str">
-        <f aca="false">IF(OR(D93="",E93=""),"",IF(D93&lt;&gt;INT(D93),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D93,"00")&amp;TEXT(E93,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B94" s="18"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="18"/>
-      <c r="E94" s="18"/>
-      <c r="F94" s="18"/>
-      <c r="G94" s="18"/>
-      <c r="H94" s="18"/>
-      <c r="I94" s="18"/>
-      <c r="J94" s="18"/>
-      <c r="K94" s="18"/>
-      <c r="L94" s="19" t="str">
-        <f aca="false">IF(OR(D94="",E94=""),"",IF(D94&lt;&gt;INT(D94),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D94,"00")&amp;TEXT(E94,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B95" s="18"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="18"/>
-      <c r="H95" s="18"/>
-      <c r="I95" s="18"/>
-      <c r="J95" s="18"/>
-      <c r="K95" s="18"/>
-      <c r="L95" s="19" t="str">
-        <f aca="false">IF(OR(D95="",E95=""),"",IF(D95&lt;&gt;INT(D95),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D95,"00")&amp;TEXT(E95,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B96" s="18"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="18"/>
-      <c r="E96" s="18"/>
-      <c r="F96" s="18"/>
-      <c r="G96" s="18"/>
-      <c r="H96" s="18"/>
-      <c r="I96" s="18"/>
-      <c r="J96" s="18"/>
-      <c r="K96" s="18"/>
-      <c r="L96" s="19" t="str">
-        <f aca="false">IF(OR(D96="",E96=""),"",IF(D96&lt;&gt;INT(D96),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D96,"00")&amp;TEXT(E96,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="18"/>
-      <c r="H97" s="18"/>
-      <c r="I97" s="18"/>
-      <c r="J97" s="18"/>
-      <c r="K97" s="18"/>
-      <c r="L97" s="19" t="str">
-        <f aca="false">IF(OR(D97="",E97=""),"",IF(D97&lt;&gt;INT(D97),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D97,"00")&amp;TEXT(E97,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B98" s="18"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="18"/>
-      <c r="E98" s="18"/>
-      <c r="F98" s="18"/>
-      <c r="G98" s="18"/>
-      <c r="H98" s="18"/>
-      <c r="I98" s="18"/>
-      <c r="J98" s="18"/>
-      <c r="K98" s="18"/>
-      <c r="L98" s="19" t="str">
-        <f aca="false">IF(OR(D98="",E98=""),"",IF(D98&lt;&gt;INT(D98),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D98,"00")&amp;TEXT(E98,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B99" s="18"/>
-      <c r="C99" s="18"/>
-      <c r="D99" s="18"/>
-      <c r="E99" s="18"/>
-      <c r="F99" s="18"/>
-      <c r="G99" s="18"/>
-      <c r="H99" s="18"/>
-      <c r="I99" s="18"/>
-      <c r="J99" s="18"/>
-      <c r="K99" s="18"/>
-      <c r="L99" s="19" t="str">
-        <f aca="false">IF(OR(D99="",E99=""),"",IF(D99&lt;&gt;INT(D99),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D99,"00")&amp;TEXT(E99,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B100" s="18"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="18"/>
-      <c r="E100" s="18"/>
-      <c r="F100" s="18"/>
-      <c r="G100" s="18"/>
-      <c r="H100" s="18"/>
-      <c r="I100" s="18"/>
-      <c r="J100" s="18"/>
-      <c r="K100" s="18"/>
-      <c r="L100" s="19" t="str">
-        <f aca="false">IF(OR(D100="",E100=""),"",IF(D100&lt;&gt;INT(D100),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D100,"00")&amp;TEXT(E100,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B101" s="18"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="18"/>
-      <c r="E101" s="18"/>
-      <c r="F101" s="18"/>
-      <c r="G101" s="18"/>
-      <c r="H101" s="18"/>
-      <c r="I101" s="18"/>
-      <c r="J101" s="18"/>
-      <c r="K101" s="18"/>
-      <c r="L101" s="19" t="str">
-        <f aca="false">IF(OR(D101="",E101=""),"",IF(D101&lt;&gt;INT(D101),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D101,"00")&amp;TEXT(E101,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B102" s="18"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="18"/>
-      <c r="F102" s="18"/>
-      <c r="G102" s="18"/>
-      <c r="H102" s="18"/>
-      <c r="I102" s="18"/>
-      <c r="J102" s="18"/>
-      <c r="K102" s="18"/>
-      <c r="L102" s="19" t="str">
-        <f aca="false">IF(OR(D102="",E102=""),"",IF(D102&lt;&gt;INT(D102),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D102,"00")&amp;TEXT(E102,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B103" s="18"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="18"/>
-      <c r="E103" s="18"/>
-      <c r="F103" s="18"/>
-      <c r="G103" s="18"/>
-      <c r="H103" s="18"/>
-      <c r="I103" s="18"/>
-      <c r="J103" s="18"/>
-      <c r="K103" s="18"/>
-      <c r="L103" s="19" t="str">
-        <f aca="false">IF(OR(D103="",E103=""),"",IF(D103&lt;&gt;INT(D103),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D103,"00")&amp;TEXT(E103,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B104" s="18"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="18"/>
-      <c r="E104" s="18"/>
-      <c r="F104" s="18"/>
-      <c r="G104" s="18"/>
-      <c r="H104" s="18"/>
-      <c r="I104" s="18"/>
-      <c r="J104" s="18"/>
-      <c r="K104" s="18"/>
-      <c r="L104" s="19" t="str">
-        <f aca="false">IF(OR(D104="",E104=""),"",IF(D104&lt;&gt;INT(D104),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D104,"00")&amp;TEXT(E104,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B105" s="18"/>
-      <c r="C105" s="18"/>
-      <c r="D105" s="18"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="18"/>
-      <c r="G105" s="18"/>
-      <c r="H105" s="18"/>
-      <c r="I105" s="18"/>
-      <c r="J105" s="18"/>
-      <c r="K105" s="18"/>
-      <c r="L105" s="19" t="str">
-        <f aca="false">IF(OR(D105="",E105=""),"",IF(D105&lt;&gt;INT(D105),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D105,"00")&amp;TEXT(E105,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B106" s="18"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="18"/>
-      <c r="E106" s="18"/>
-      <c r="F106" s="18"/>
-      <c r="G106" s="18"/>
-      <c r="H106" s="18"/>
-      <c r="I106" s="18"/>
-      <c r="J106" s="18"/>
-      <c r="K106" s="18"/>
-      <c r="L106" s="19" t="str">
-        <f aca="false">IF(OR(D106="",E106=""),"",IF(D106&lt;&gt;INT(D106),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D106,"00")&amp;TEXT(E106,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B107" s="18"/>
-      <c r="C107" s="18"/>
-      <c r="D107" s="18"/>
-      <c r="E107" s="18"/>
-      <c r="F107" s="18"/>
-      <c r="G107" s="18"/>
-      <c r="H107" s="18"/>
-      <c r="I107" s="18"/>
-      <c r="J107" s="18"/>
-      <c r="K107" s="18"/>
-      <c r="L107" s="19" t="str">
-        <f aca="false">IF(OR(D107="",E107=""),"",IF(D107&lt;&gt;INT(D107),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D107,"00")&amp;TEXT(E107,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B110" s="14" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B130" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C130" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D130" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E130" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F130" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G130" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H130" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I130" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J130" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K130" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L130" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B131" s="18"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="18"/>
-      <c r="H131" s="18"/>
-      <c r="I131" s="18"/>
-      <c r="J131" s="18"/>
-      <c r="K131" s="18"/>
-      <c r="L131" s="19" t="str">
-        <f aca="false">IF(OR(D131="",E131=""),"",IF(D131&lt;&gt;INT(D131),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D131,"00")&amp;TEXT(E131,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B132" s="18"/>
-      <c r="C132" s="18"/>
-      <c r="D132" s="18"/>
-      <c r="E132" s="18"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="18"/>
-      <c r="H132" s="18"/>
-      <c r="I132" s="18"/>
-      <c r="J132" s="18"/>
-      <c r="K132" s="18"/>
-      <c r="L132" s="19" t="str">
-        <f aca="false">IF(OR(D132="",E132=""),"",IF(D132&lt;&gt;INT(D132),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D132,"00")&amp;TEXT(E132,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B133" s="18"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="18"/>
-      <c r="E133" s="18"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="18"/>
-      <c r="H133" s="18"/>
-      <c r="I133" s="18"/>
-      <c r="J133" s="18"/>
-      <c r="K133" s="18"/>
-      <c r="L133" s="19" t="str">
-        <f aca="false">IF(OR(D133="",E133=""),"",IF(D133&lt;&gt;INT(D133),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D133,"00")&amp;TEXT(E133,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B134" s="18"/>
-      <c r="C134" s="18"/>
-      <c r="D134" s="18"/>
-      <c r="E134" s="18"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="18"/>
-      <c r="H134" s="18"/>
-      <c r="I134" s="18"/>
-      <c r="J134" s="18"/>
-      <c r="K134" s="18"/>
-      <c r="L134" s="19" t="str">
-        <f aca="false">IF(OR(D134="",E134=""),"",IF(D134&lt;&gt;INT(D134),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D134,"00")&amp;TEXT(E134,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B135" s="18"/>
-      <c r="C135" s="18"/>
-      <c r="D135" s="18"/>
-      <c r="E135" s="18"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="18"/>
-      <c r="H135" s="18"/>
-      <c r="I135" s="18"/>
-      <c r="J135" s="18"/>
-      <c r="K135" s="18"/>
-      <c r="L135" s="19" t="str">
-        <f aca="false">IF(OR(D135="",E135=""),"",IF(D135&lt;&gt;INT(D135),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D135,"00")&amp;TEXT(E135,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B136" s="18"/>
-      <c r="C136" s="18"/>
-      <c r="D136" s="18"/>
-      <c r="E136" s="18"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="18"/>
-      <c r="H136" s="18"/>
-      <c r="I136" s="18"/>
-      <c r="J136" s="18"/>
-      <c r="K136" s="18"/>
-      <c r="L136" s="19" t="str">
-        <f aca="false">IF(OR(D136="",E136=""),"",IF(D136&lt;&gt;INT(D136),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D136,"00")&amp;TEXT(E136,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B137" s="18"/>
-      <c r="C137" s="18"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="18"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="18"/>
-      <c r="H137" s="18"/>
-      <c r="I137" s="18"/>
-      <c r="J137" s="18"/>
-      <c r="K137" s="18"/>
-      <c r="L137" s="19" t="str">
-        <f aca="false">IF(OR(D137="",E137=""),"",IF(D137&lt;&gt;INT(D137),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D137,"00")&amp;TEXT(E137,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B138" s="18"/>
-      <c r="C138" s="18"/>
-      <c r="D138" s="18"/>
-      <c r="E138" s="18"/>
-      <c r="F138" s="18"/>
-      <c r="G138" s="18"/>
-      <c r="H138" s="18"/>
-      <c r="I138" s="18"/>
-      <c r="J138" s="18"/>
-      <c r="K138" s="18"/>
-      <c r="L138" s="19" t="str">
-        <f aca="false">IF(OR(D138="",E138=""),"",IF(D138&lt;&gt;INT(D138),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D138,"00")&amp;TEXT(E138,"000")))</f>
         <v/>
       </c>
     </row>
@@ -11867,7 +8467,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L167"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -11879,7 +8479,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11890,53 +8490,53 @@
         <v>23</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="F28" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="G28" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="H28" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="I28" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="J28" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="K28" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H28" s="16" t="s">
+      <c r="L28" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12207,48 +8807,48 @@
     </row>
     <row r="45" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E69" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="F69" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="G69" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="H69" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E69" s="16" t="s">
+      <c r="I69" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F69" s="16" t="s">
+      <c r="J69" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G69" s="16" t="s">
+      <c r="K69" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="L69" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I69" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J69" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K69" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L69" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12519,48 +9119,48 @@
     </row>
     <row r="86" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B110" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D110" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E110" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B110" s="16" t="s">
+      <c r="F110" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C110" s="16" t="s">
+      <c r="G110" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D110" s="16" t="s">
+      <c r="H110" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E110" s="16" t="s">
+      <c r="I110" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F110" s="16" t="s">
+      <c r="J110" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G110" s="16" t="s">
+      <c r="K110" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H110" s="16" t="s">
+      <c r="L110" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I110" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J110" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K110" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L110" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12831,72 +9431,175 @@
     </row>
     <row r="127" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B137" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C137" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B127" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="15" t="s">
+      <c r="D137" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E137" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B151" s="16" t="s">
+      <c r="F137" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C151" s="16" t="s">
+      <c r="G137" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D151" s="16" t="s">
+      <c r="H137" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E151" s="16" t="s">
+      <c r="I137" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F151" s="16" t="s">
+      <c r="J137" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G151" s="16" t="s">
+      <c r="K137" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H151" s="16" t="s">
+      <c r="L137" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I151" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J151" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K151" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L151" s="16" t="s">
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B138" s="18"/>
+      <c r="C138" s="18"/>
+      <c r="D138" s="18"/>
+      <c r="E138" s="18"/>
+      <c r="F138" s="18"/>
+      <c r="G138" s="18"/>
+      <c r="H138" s="18"/>
+      <c r="I138" s="18"/>
+      <c r="J138" s="18"/>
+      <c r="K138" s="18"/>
+      <c r="L138" s="19" t="str">
+        <f aca="false">IF(OR(D138="",E138=""),"",IF(D138&lt;&gt;INT(D138),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D138,"00")&amp;TEXT(E138,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="18"/>
+      <c r="F139" s="18"/>
+      <c r="G139" s="18"/>
+      <c r="H139" s="18"/>
+      <c r="I139" s="18"/>
+      <c r="J139" s="18"/>
+      <c r="K139" s="18"/>
+      <c r="L139" s="19" t="str">
+        <f aca="false">IF(OR(D139="",E139=""),"",IF(D139&lt;&gt;INT(D139),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D139,"00")&amp;TEXT(E139,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B140" s="18"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="18"/>
+      <c r="G140" s="18"/>
+      <c r="H140" s="18"/>
+      <c r="I140" s="18"/>
+      <c r="J140" s="18"/>
+      <c r="K140" s="18"/>
+      <c r="L140" s="19" t="str">
+        <f aca="false">IF(OR(D140="",E140=""),"",IF(D140&lt;&gt;INT(D140),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D140,"00")&amp;TEXT(E140,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B141" s="18"/>
+      <c r="C141" s="18"/>
+      <c r="D141" s="18"/>
+      <c r="E141" s="18"/>
+      <c r="F141" s="18"/>
+      <c r="G141" s="18"/>
+      <c r="H141" s="18"/>
+      <c r="I141" s="18"/>
+      <c r="J141" s="18"/>
+      <c r="K141" s="18"/>
+      <c r="L141" s="19" t="str">
+        <f aca="false">IF(OR(D141="",E141=""),"",IF(D141&lt;&gt;INT(D141),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D141,"00")&amp;TEXT(E141,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B144" s="14" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B152" s="18"/>
-      <c r="C152" s="18"/>
-      <c r="D152" s="18"/>
-      <c r="E152" s="18"/>
-      <c r="F152" s="18"/>
-      <c r="G152" s="18"/>
-      <c r="H152" s="18"/>
-      <c r="I152" s="18"/>
-      <c r="J152" s="18"/>
-      <c r="K152" s="18"/>
-      <c r="L152" s="19" t="str">
-        <f aca="false">IF(OR(D152="",E152=""),"",IF(D152&lt;&gt;INT(D152),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D152,"00")&amp;TEXT(E152,"000")))</f>
-        <v/>
+      <c r="A152" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B152" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D152" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E152" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F152" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G152" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H152" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I152" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="J152" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="K152" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L152" s="16" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B153" s="18"/>
       <c r="C153" s="18"/>
@@ -12915,7 +9618,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B154" s="18"/>
       <c r="C154" s="18"/>
@@ -12932,502 +9635,87 @@
         <v/>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B155" s="18"/>
-      <c r="C155" s="18"/>
-      <c r="D155" s="18"/>
-      <c r="E155" s="18"/>
-      <c r="F155" s="18"/>
-      <c r="G155" s="18"/>
-      <c r="H155" s="18"/>
-      <c r="I155" s="18"/>
-      <c r="J155" s="18"/>
-      <c r="K155" s="18"/>
-      <c r="L155" s="19" t="str">
-        <f aca="false">IF(OR(D155="",E155=""),"",IF(D155&lt;&gt;INT(D155),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D155,"00")&amp;TEXT(E155,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B156" s="18"/>
-      <c r="C156" s="18"/>
-      <c r="D156" s="18"/>
-      <c r="E156" s="18"/>
-      <c r="F156" s="18"/>
-      <c r="G156" s="18"/>
-      <c r="H156" s="18"/>
-      <c r="I156" s="18"/>
-      <c r="J156" s="18"/>
-      <c r="K156" s="18"/>
-      <c r="L156" s="19" t="str">
-        <f aca="false">IF(OR(D156="",E156=""),"",IF(D156&lt;&gt;INT(D156),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D156,"00")&amp;TEXT(E156,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B157" s="18"/>
-      <c r="C157" s="18"/>
-      <c r="D157" s="18"/>
-      <c r="E157" s="18"/>
-      <c r="F157" s="18"/>
-      <c r="G157" s="18"/>
-      <c r="H157" s="18"/>
-      <c r="I157" s="18"/>
-      <c r="J157" s="18"/>
-      <c r="K157" s="18"/>
-      <c r="L157" s="19" t="str">
-        <f aca="false">IF(OR(D157="",E157=""),"",IF(D157&lt;&gt;INT(D157),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D157,"00")&amp;TEXT(E157,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B158" s="18"/>
-      <c r="C158" s="18"/>
-      <c r="D158" s="18"/>
-      <c r="E158" s="18"/>
-      <c r="F158" s="18"/>
-      <c r="G158" s="18"/>
-      <c r="H158" s="18"/>
-      <c r="I158" s="18"/>
-      <c r="J158" s="18"/>
-      <c r="K158" s="18"/>
-      <c r="L158" s="19" t="str">
-        <f aca="false">IF(OR(D158="",E158=""),"",IF(D158&lt;&gt;INT(D158),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D158,"00")&amp;TEXT(E158,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B159" s="18"/>
-      <c r="C159" s="18"/>
-      <c r="D159" s="18"/>
-      <c r="E159" s="18"/>
-      <c r="F159" s="18"/>
-      <c r="G159" s="18"/>
-      <c r="H159" s="18"/>
-      <c r="I159" s="18"/>
-      <c r="J159" s="18"/>
-      <c r="K159" s="18"/>
-      <c r="L159" s="19" t="str">
-        <f aca="false">IF(OR(D159="",E159=""),"",IF(D159&lt;&gt;INT(D159),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D159,"00")&amp;TEXT(E159,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B160" s="18"/>
-      <c r="C160" s="18"/>
-      <c r="D160" s="18"/>
-      <c r="E160" s="18"/>
-      <c r="F160" s="18"/>
-      <c r="G160" s="18"/>
-      <c r="H160" s="18"/>
-      <c r="I160" s="18"/>
-      <c r="J160" s="18"/>
-      <c r="K160" s="18"/>
-      <c r="L160" s="19" t="str">
-        <f aca="false">IF(OR(D160="",E160=""),"",IF(D160&lt;&gt;INT(D160),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D160,"00")&amp;TEXT(E160,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B161" s="18"/>
-      <c r="C161" s="18"/>
-      <c r="D161" s="18"/>
-      <c r="E161" s="18"/>
-      <c r="F161" s="18"/>
-      <c r="G161" s="18"/>
-      <c r="H161" s="18"/>
-      <c r="I161" s="18"/>
-      <c r="J161" s="18"/>
-      <c r="K161" s="18"/>
-      <c r="L161" s="19" t="str">
-        <f aca="false">IF(OR(D161="",E161=""),"",IF(D161&lt;&gt;INT(D161),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D161,"00")&amp;TEXT(E161,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B162" s="18"/>
-      <c r="C162" s="18"/>
-      <c r="D162" s="18"/>
-      <c r="E162" s="18"/>
-      <c r="F162" s="18"/>
-      <c r="G162" s="18"/>
-      <c r="H162" s="18"/>
-      <c r="I162" s="18"/>
-      <c r="J162" s="18"/>
-      <c r="K162" s="18"/>
-      <c r="L162" s="19" t="str">
-        <f aca="false">IF(OR(D162="",E162=""),"",IF(D162&lt;&gt;INT(D162),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D162,"00")&amp;TEXT(E162,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B163" s="18"/>
-      <c r="C163" s="18"/>
-      <c r="D163" s="18"/>
-      <c r="E163" s="18"/>
-      <c r="F163" s="18"/>
-      <c r="G163" s="18"/>
-      <c r="H163" s="18"/>
-      <c r="I163" s="18"/>
-      <c r="J163" s="18"/>
-      <c r="K163" s="18"/>
-      <c r="L163" s="19" t="str">
-        <f aca="false">IF(OR(D163="",E163=""),"",IF(D163&lt;&gt;INT(D163),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D163,"00")&amp;TEXT(E163,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B164" s="18"/>
-      <c r="C164" s="18"/>
-      <c r="D164" s="18"/>
-      <c r="E164" s="18"/>
-      <c r="F164" s="18"/>
-      <c r="G164" s="18"/>
-      <c r="H164" s="18"/>
-      <c r="I164" s="18"/>
-      <c r="J164" s="18"/>
-      <c r="K164" s="18"/>
-      <c r="L164" s="19" t="str">
-        <f aca="false">IF(OR(D164="",E164=""),"",IF(D164&lt;&gt;INT(D164),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D164,"00")&amp;TEXT(E164,"000")))</f>
-        <v/>
+    <row r="157" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B157" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B165" s="18"/>
-      <c r="C165" s="18"/>
-      <c r="D165" s="18"/>
-      <c r="E165" s="18"/>
-      <c r="F165" s="18"/>
-      <c r="G165" s="18"/>
-      <c r="H165" s="18"/>
-      <c r="I165" s="18"/>
-      <c r="J165" s="18"/>
-      <c r="K165" s="18"/>
-      <c r="L165" s="19" t="str">
-        <f aca="false">IF(OR(D165="",E165=""),"",IF(D165&lt;&gt;INT(D165),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D165,"00")&amp;TEXT(E165,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7" t="s">
+      <c r="A165" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B165" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C165" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B168" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="15" t="s">
+      <c r="D165" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E165" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B178" s="16" t="s">
+      <c r="F165" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C178" s="16" t="s">
+      <c r="G165" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D178" s="16" t="s">
+      <c r="H165" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E178" s="16" t="s">
+      <c r="I165" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F178" s="16" t="s">
+      <c r="J165" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G178" s="16" t="s">
+      <c r="K165" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H178" s="16" t="s">
+      <c r="L165" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I178" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J178" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K178" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L178" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="17" t="n">
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B179" s="18"/>
-      <c r="C179" s="18"/>
-      <c r="D179" s="18"/>
-      <c r="E179" s="18"/>
-      <c r="F179" s="18"/>
-      <c r="G179" s="18"/>
-      <c r="H179" s="18"/>
-      <c r="I179" s="18"/>
-      <c r="J179" s="18"/>
-      <c r="K179" s="18"/>
-      <c r="L179" s="19" t="str">
-        <f aca="false">IF(OR(D179="",E179=""),"",IF(D179&lt;&gt;INT(D179),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D179,"00")&amp;TEXT(E179,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="17" t="n">
+      <c r="B166" s="18"/>
+      <c r="C166" s="18"/>
+      <c r="D166" s="18"/>
+      <c r="E166" s="18"/>
+      <c r="F166" s="18"/>
+      <c r="G166" s="18"/>
+      <c r="H166" s="18"/>
+      <c r="I166" s="18"/>
+      <c r="J166" s="18"/>
+      <c r="K166" s="18"/>
+      <c r="L166" s="19" t="str">
+        <f aca="false">IF(OR(D166="",E166=""),"",IF(D166&lt;&gt;INT(D166),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D166,"00")&amp;TEXT(E166,"000")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B180" s="18"/>
-      <c r="C180" s="18"/>
-      <c r="D180" s="18"/>
-      <c r="E180" s="18"/>
-      <c r="F180" s="18"/>
-      <c r="G180" s="18"/>
-      <c r="H180" s="18"/>
-      <c r="I180" s="18"/>
-      <c r="J180" s="18"/>
-      <c r="K180" s="18"/>
-      <c r="L180" s="19" t="str">
-        <f aca="false">IF(OR(D180="",E180=""),"",IF(D180&lt;&gt;INT(D180),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D180,"00")&amp;TEXT(E180,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B181" s="18"/>
-      <c r="C181" s="18"/>
-      <c r="D181" s="18"/>
-      <c r="E181" s="18"/>
-      <c r="F181" s="18"/>
-      <c r="G181" s="18"/>
-      <c r="H181" s="18"/>
-      <c r="I181" s="18"/>
-      <c r="J181" s="18"/>
-      <c r="K181" s="18"/>
-      <c r="L181" s="19" t="str">
-        <f aca="false">IF(OR(D181="",E181=""),"",IF(D181&lt;&gt;INT(D181),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D181,"00")&amp;TEXT(E181,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B182" s="18"/>
-      <c r="C182" s="18"/>
-      <c r="D182" s="18"/>
-      <c r="E182" s="18"/>
-      <c r="F182" s="18"/>
-      <c r="G182" s="18"/>
-      <c r="H182" s="18"/>
-      <c r="I182" s="18"/>
-      <c r="J182" s="18"/>
-      <c r="K182" s="18"/>
-      <c r="L182" s="19" t="str">
-        <f aca="false">IF(OR(D182="",E182=""),"",IF(D182&lt;&gt;INT(D182),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D182,"00")&amp;TEXT(E182,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B185" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B193" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C193" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D193" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E193" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F193" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G193" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H193" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I193" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J193" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K193" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L193" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B194" s="18"/>
-      <c r="C194" s="18"/>
-      <c r="D194" s="18"/>
-      <c r="E194" s="18"/>
-      <c r="F194" s="18"/>
-      <c r="G194" s="18"/>
-      <c r="H194" s="18"/>
-      <c r="I194" s="18"/>
-      <c r="J194" s="18"/>
-      <c r="K194" s="18"/>
-      <c r="L194" s="19" t="str">
-        <f aca="false">IF(OR(D194="",E194=""),"",IF(D194&lt;&gt;INT(D194),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D194,"00")&amp;TEXT(E194,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B195" s="18"/>
-      <c r="C195" s="18"/>
-      <c r="D195" s="18"/>
-      <c r="E195" s="18"/>
-      <c r="F195" s="18"/>
-      <c r="G195" s="18"/>
-      <c r="H195" s="18"/>
-      <c r="I195" s="18"/>
-      <c r="J195" s="18"/>
-      <c r="K195" s="18"/>
-      <c r="L195" s="19" t="str">
-        <f aca="false">IF(OR(D195="",E195=""),"",IF(D195&lt;&gt;INT(D195),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D195,"00")&amp;TEXT(E195,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B198" s="14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B206" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C206" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D206" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E206" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F206" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G206" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H206" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I206" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J206" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K206" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L206" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B207" s="18"/>
-      <c r="C207" s="18"/>
-      <c r="D207" s="18"/>
-      <c r="E207" s="18"/>
-      <c r="F207" s="18"/>
-      <c r="G207" s="18"/>
-      <c r="H207" s="18"/>
-      <c r="I207" s="18"/>
-      <c r="J207" s="18"/>
-      <c r="K207" s="18"/>
-      <c r="L207" s="19" t="str">
-        <f aca="false">IF(OR(D207="",E207=""),"",IF(D207&lt;&gt;INT(D207),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D207,"00")&amp;TEXT(E207,"000")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B208" s="18"/>
-      <c r="C208" s="18"/>
-      <c r="D208" s="18"/>
-      <c r="E208" s="18"/>
-      <c r="F208" s="18"/>
-      <c r="G208" s="18"/>
-      <c r="H208" s="18"/>
-      <c r="I208" s="18"/>
-      <c r="J208" s="18"/>
-      <c r="K208" s="18"/>
-      <c r="L208" s="19" t="str">
-        <f aca="false">IF(OR(D208="",E208=""),"",IF(D208&lt;&gt;INT(D208),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D208,"00")&amp;TEXT(E208,"000")))</f>
+      <c r="B167" s="18"/>
+      <c r="C167" s="18"/>
+      <c r="D167" s="18"/>
+      <c r="E167" s="18"/>
+      <c r="F167" s="18"/>
+      <c r="G167" s="18"/>
+      <c r="H167" s="18"/>
+      <c r="I167" s="18"/>
+      <c r="J167" s="18"/>
+      <c r="K167" s="18"/>
+      <c r="L167" s="19" t="str">
+        <f aca="false">IF(OR(D167="",E167=""),"",IF(D167&lt;&gt;INT(D167),"⚠需定義",$B$2&amp;"-"&amp;TEXT(D167,"00")&amp;TEXT(E167,"000")))</f>
         <v/>
       </c>
     </row>
@@ -13460,7 +9748,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13471,53 +9759,53 @@
         <v>25</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="F21" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="G21" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="H21" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="I21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="J21" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="K21" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="L21" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13674,48 +9962,48 @@
     </row>
     <row r="32" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="F49" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="G49" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="H49" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="I49" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="16" t="s">
+      <c r="J49" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G49" s="16" t="s">
+      <c r="K49" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="L49" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I49" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J49" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K49" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L49" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13872,48 +10160,48 @@
     </row>
     <row r="60" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="F77" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="G77" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D77" s="16" t="s">
+      <c r="H77" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E77" s="16" t="s">
+      <c r="I77" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F77" s="16" t="s">
+      <c r="J77" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G77" s="16" t="s">
+      <c r="K77" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H77" s="16" t="s">
+      <c r="L77" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I77" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J77" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K77" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L77" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14097,7 +10385,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14108,53 +10396,53 @@
         <v>27</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>82</v>
+        <v>53</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="G13" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="H13" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="I13" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="J13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="K13" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14224,7 +10512,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14235,53 +10523,53 @@
         <v>29</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>84</v>
+        <v>53</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="F62" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="G62" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D62" s="16" t="s">
+      <c r="H62" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E62" s="16" t="s">
+      <c r="I62" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F62" s="16" t="s">
+      <c r="J62" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G62" s="16" t="s">
+      <c r="K62" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H62" s="16" t="s">
+      <c r="L62" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I62" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J62" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K62" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L62" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15016,7 +11304,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15027,53 +11315,53 @@
         <v>35</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="F49" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="G49" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="H49" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="I49" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="16" t="s">
+      <c r="J49" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G49" s="16" t="s">
+      <c r="K49" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="L49" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I49" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J49" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K49" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L49" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15781,48 +12069,48 @@
     </row>
     <row r="89" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B134" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D134" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E134" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B134" s="16" t="s">
+      <c r="F134" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C134" s="16" t="s">
+      <c r="G134" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D134" s="16" t="s">
+      <c r="H134" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E134" s="16" t="s">
+      <c r="I134" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F134" s="16" t="s">
+      <c r="J134" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G134" s="16" t="s">
+      <c r="K134" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H134" s="16" t="s">
+      <c r="L134" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I134" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J134" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K134" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L134" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16530,48 +12818,48 @@
     </row>
     <row r="174" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B181" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C181" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D181" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E181" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B181" s="16" t="s">
+      <c r="F181" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C181" s="16" t="s">
+      <c r="G181" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D181" s="16" t="s">
+      <c r="H181" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E181" s="16" t="s">
+      <c r="I181" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F181" s="16" t="s">
+      <c r="J181" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G181" s="16" t="s">
+      <c r="K181" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H181" s="16" t="s">
+      <c r="L181" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I181" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J181" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K181" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L181" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16641,7 +12929,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16652,53 +12940,53 @@
         <v>37</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>90</v>
+        <v>53</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="F64" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="G64" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="H64" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E64" s="16" t="s">
+      <c r="I64" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F64" s="16" t="s">
+      <c r="J64" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G64" s="16" t="s">
+      <c r="K64" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H64" s="16" t="s">
+      <c r="L64" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I64" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J64" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K64" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L64" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17547,7 +13835,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17558,53 +13846,53 @@
         <v>33</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>92</v>
+        <v>53</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="F65" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="G65" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="H65" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="I65" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F65" s="16" t="s">
+      <c r="J65" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G65" s="16" t="s">
+      <c r="K65" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="L65" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I65" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J65" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K65" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L65" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18377,7 +14665,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18388,53 +14676,53 @@
         <v>43</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="F16" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="G16" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="H16" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="I16" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="J16" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="K16" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="L16" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18591,48 +14879,48 @@
     </row>
     <row r="27" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="F38" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="G38" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="H38" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="I38" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="J38" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="K38" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="L38" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L38" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18751,48 +15039,48 @@
     </row>
     <row r="47" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="F58" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="G58" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D58" s="16" t="s">
+      <c r="H58" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E58" s="16" t="s">
+      <c r="I58" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="16" t="s">
+      <c r="J58" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G58" s="16" t="s">
+      <c r="K58" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="L58" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I58" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J58" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K58" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L58" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18911,48 +15199,48 @@
     </row>
     <row r="67" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E79" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="F79" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="G79" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D79" s="16" t="s">
+      <c r="H79" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E79" s="16" t="s">
+      <c r="I79" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F79" s="16" t="s">
+      <c r="J79" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G79" s="16" t="s">
+      <c r="K79" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H79" s="16" t="s">
+      <c r="L79" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="I79" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J79" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K79" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L79" s="16" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
